--- a/NCU_Mens_Master_ID_Mapping.xlsx
+++ b/NCU_Mens_Master_ID_Mapping.xlsx
@@ -71825,12 +71825,12 @@
       </c>
       <c r="C2231" t="inlineStr">
         <is>
-          <t>Fuzzy Match (100%)</t>
+          <t>Manual Override</t>
         </is>
       </c>
       <c r="D2231" t="inlineStr">
         <is>
-          <t>2021122966</t>
+          <t>2021114327</t>
         </is>
       </c>
       <c r="E2231" t="inlineStr">
@@ -71840,7 +71840,7 @@
       </c>
       <c r="F2231" t="inlineStr">
         <is>
-          <t>Carrickfergus Cricket Club</t>
+          <t>North Down Cricket Club</t>
         </is>
       </c>
     </row>
@@ -71857,12 +71857,12 @@
       </c>
       <c r="C2232" t="inlineStr">
         <is>
-          <t>Fuzzy Match (100%)</t>
+          <t>Manual Override</t>
         </is>
       </c>
       <c r="D2232" t="inlineStr">
         <is>
-          <t>2021122966</t>
+          <t>2021114327</t>
         </is>
       </c>
       <c r="E2232" t="inlineStr">
@@ -71872,7 +71872,7 @@
       </c>
       <c r="F2232" t="inlineStr">
         <is>
-          <t>Carrickfergus Cricket Club</t>
+          <t>North Down Cricket Club</t>
         </is>
       </c>
     </row>
